--- a/sellers/sunsu-commerce/outputs/순수커머스_전체유니콘상품_KC최종.xlsx
+++ b/sellers/sunsu-commerce/outputs/순수커머스_전체유니콘상품_KC최종.xlsx
@@ -13,8 +13,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체 유니콘 상품'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요약'!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'검증 로그'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요약'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'검증 로그'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -63,7 +63,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>수집 완료 수</t>
+          <t>수집 상품 수</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -587,7 +587,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>수집 실패 수</t>
+          <t>유니콘 상품 수</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -597,7 +597,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>유니콘 확정</t>
+          <t>KC 있음</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -607,7 +607,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>유니콘 고신뢰 추론</t>
+          <t>KC 적합</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -617,7 +617,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KC 있음</t>
+          <t>KC 기간만료</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -627,7 +627,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KC 적합</t>
+          <t>KC 공개표기 없음</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -637,7 +637,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KC 기간만료</t>
+          <t>검증 불가</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -647,35 +647,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KC 공개표기 없음</t>
+          <t>중복 수</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>검증 불가</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>중복 수</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -686,7 +666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -695,7 +675,6 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -706,7 +685,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>상품명</t>
+          <t>단계</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -716,7 +695,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>근거 유형</t>
+          <t>이유</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -726,17 +705,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>제외 사유</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
           <t>확인 날짜</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>